--- a/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_5.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_5.xlsx
@@ -8960,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -9045,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -9079,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
